--- a/demo_data/sectors/toptan_ticaret/inventory.xlsx
+++ b/demo_data/sectors/toptan_ticaret/inventory.xlsx
@@ -482,7 +482,7 @@
         <v>850</v>
       </c>
       <c r="E2" t="n">
-        <v>811894.5</v>
+        <v>811895.58</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>46012</v>
